--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD83E76-73A2-FC42-8C20-3102113B82CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3C7D0C-C119-9246-9F3D-1CB7029BCE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12680" yWindow="500" windowWidth="24320" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="24320" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -326,6 +326,24 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -664,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1104,44 +1122,47 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39">
-        <v>55</v>
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>100</v>
@@ -1149,161 +1170,182 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="B42">
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45">
-        <v>142</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>74</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="B48">
+        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B49">
-        <v>31.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>77</v>
+      </c>
+      <c r="B52">
+        <v>31.6</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A98F2B-D508-A947-84CA-9C825522F982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA94A428-7E4E-7945-A021-77DFD249B31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="740" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34360" yWindow="-26480" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -323,21 +323,12 @@
     <t>currency</t>
   </si>
   <si>
-    <t>threaded</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
     <t>estimated axle crown 493.75</t>
   </si>
   <si>
-    <t>100 mm w 25% sag</t>
-  </si>
-  <si>
-    <t>120 mm w 25% sag</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -360,6 +351,18 @@
   </si>
   <si>
     <t>a8:f34</t>
+  </si>
+  <si>
+    <t>threaded 68</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>100 mm w 20% sag</t>
+  </si>
+  <si>
+    <t>120 mm w 20% sag</t>
   </si>
 </sst>
 </file>
@@ -749,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -1037,7 +1040,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -1050,7 +1053,7 @@
         <v>45</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -1058,11 +1061,11 @@
         <v>46</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H25">
-        <f>501-0.25*100</f>
-        <v>476</v>
+        <f>501-0.2*100</f>
+        <v>481</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -1070,11 +1073,11 @@
         <v>47</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H26">
-        <f>521-0.25*120</f>
-        <v>491</v>
+        <f>521-0.2*120</f>
+        <v>497</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1166,26 +1169,26 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -1249,18 +1252,24 @@
       <c r="A49" t="s">
         <v>70</v>
       </c>
+      <c r="B49">
+        <v>142</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>71</v>
       </c>
+      <c r="B50">
+        <v>100</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>72</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1281,7 +1290,7 @@
         <v>75</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -1336,55 +1345,73 @@
       <c r="A64" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B71">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>95</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA94A428-7E4E-7945-A021-77DFD249B31D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B00DD9-3A7E-BF4C-9FC5-12E7672CF2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34360" yWindow="-26480" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1237,6 +1237,9 @@
       <c r="A46" t="s">
         <v>67</v>
       </c>
+      <c r="B46">
+        <v>120</v>
+      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B00DD9-3A7E-BF4C-9FC5-12E7672CF2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5C5B21-81F3-EF48-ADD7-4C4E59536CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34360" yWindow="-26480" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>120 mm w 20% sag</t>
+  </si>
+  <si>
+    <t>https://www.enigmabikes.com/cdn/shop/files/Explor-2025-Hero_2500x.jpg?v=1741962764</t>
   </si>
 </sst>
 </file>
@@ -747,6 +750,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5C5B21-81F3-EF48-ADD7-4C4E59536CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9483F32A-7CA2-C246-9159-2713CC66AFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34360" yWindow="-26480" windowWidth="25860" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,12 @@
   </si>
   <si>
     <t>https://www.enigmabikes.com/cdn/shop/files/Explor-2025-Hero_2500x.jpg?v=1741962764</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Hailsham, East Sussex, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -704,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1425,6 +1431,14 @@
         <v>107</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9483F32A-7CA2-C246-9159-2713CC66AFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D308D32-5B5E-0945-8BB5-1076F0211AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>Hailsham, East Sussex, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -710,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1283,159 +1301,189 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>75</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>79</v>
-      </c>
-      <c r="B58">
-        <v>160</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>86</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>87</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>85</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B71">
-        <v>3300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B72">
-        <v>5800</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>92</v>
+      </c>
+      <c r="B77">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B78">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>95</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>111</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D308D32-5B5E-0945-8BB5-1076F0211AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A67132-785F-2C48-B9A0-DCDE42392BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="500" windowWidth="24480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -350,9 +350,6 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>a8:f34</t>
-  </si>
-  <si>
     <t>threaded 68</t>
   </si>
   <si>
@@ -390,6 +387,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f36</t>
   </si>
 </sst>
 </file>
@@ -728,13 +734,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -742,7 +748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -750,7 +756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -758,7 +764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -766,7 +772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -774,23 +780,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -810,7 +813,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -829,8 +832,11 @@
       <c r="F9">
         <v>669</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -850,7 +856,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -870,7 +876,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -890,7 +896,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -910,7 +916,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -930,7 +936,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -950,7 +956,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1072,359 +1078,377 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22">
+        <v>120</v>
+      </c>
+      <c r="D22">
+        <v>120</v>
+      </c>
+      <c r="E22">
+        <v>120</v>
+      </c>
+      <c r="F22">
+        <v>120</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23">
+        <v>25</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23">
+        <v>25</v>
+      </c>
+      <c r="F23">
+        <v>25</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23">
+        <f>501-0.2*100</f>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
+      </c>
+      <c r="H24">
+        <f>521-0.2*120</f>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25">
-        <f>501-0.2*100</f>
-        <v>481</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>47</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H26">
-        <f>521-0.2*120</f>
-        <v>497</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30">
-        <v>700</v>
-      </c>
-      <c r="D30">
-        <v>700</v>
-      </c>
-      <c r="E30">
-        <v>700</v>
-      </c>
-      <c r="F30">
-        <v>700</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>52</v>
-      </c>
-      <c r="C31">
         <v>50</v>
-      </c>
-      <c r="D31">
-        <v>50</v>
-      </c>
-      <c r="E31">
-        <v>50</v>
-      </c>
-      <c r="F31">
-        <v>50</v>
-      </c>
-      <c r="G31" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>700</v>
+      </c>
+      <c r="D32">
+        <v>700</v>
+      </c>
+      <c r="E32">
+        <v>700</v>
+      </c>
+      <c r="F32">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33">
+        <v>50</v>
+      </c>
+      <c r="D33">
+        <v>50</v>
+      </c>
+      <c r="E33">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>50</v>
+      </c>
+      <c r="G33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>54</v>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>55</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>55</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>55</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>57</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>98</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B39" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>101</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B41" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B42" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>61</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>64</v>
       </c>
-      <c r="B43">
+      <c r="B45">
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>66</v>
       </c>
-      <c r="B45">
+      <c r="B47">
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>67</v>
       </c>
-      <c r="B46">
+      <c r="B48">
         <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49">
-        <v>142</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>113</v>
+        <v>70</v>
+      </c>
+      <c r="B51">
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>114</v>
+        <v>71</v>
+      </c>
+      <c r="B52">
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>72</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>74</v>
-      </c>
-      <c r="B59">
-        <v>31.6</v>
+        <v>72</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>75</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="B61">
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>79</v>
-      </c>
-      <c r="B64">
-        <v>160</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="B66">
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>85</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>86</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -1432,59 +1456,75 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>92</v>
-      </c>
-      <c r="B77">
-        <v>3300</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>93</v>
-      </c>
-      <c r="B78">
-        <v>5800</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>92</v>
+      </c>
+      <c r="B79">
+        <v>3300</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>95</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
+      </c>
+      <c r="B80">
+        <v>5800</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" t="s">
         <v>111</v>
-      </c>
-      <c r="B81" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Enigma Explor 2025.xlsx
+++ b/data/gravel/Enigma Explor 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A67132-785F-2C48-B9A0-DCDE42392BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AF876D-B060-EF44-A521-04C7947253E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="500" windowWidth="24480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9700" yWindow="500" windowWidth="24480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -326,9 +326,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>estimated axle crown 493.75</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -356,12 +353,6 @@
     <t>GBP</t>
   </si>
   <si>
-    <t>100 mm w 20% sag</t>
-  </si>
-  <si>
-    <t>120 mm w 20% sag</t>
-  </si>
-  <si>
     <t>https://www.enigmabikes.com/cdn/shop/files/Explor-2025-Hero_2500x.jpg?v=1741962764</t>
   </si>
   <si>
@@ -396,6 +387,18 @@
   </si>
   <si>
     <t>a8:f36</t>
+  </si>
+  <si>
+    <t>80-120</t>
+  </si>
+  <si>
+    <t>BSA</t>
+  </si>
+  <si>
+    <t>ZS44</t>
+  </si>
+  <si>
+    <t>EC44</t>
   </si>
 </sst>
 </file>
@@ -734,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -782,7 +785,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -790,7 +793,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -976,7 +979,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -996,7 +999,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -1076,29 +1079,27 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>120</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C23">
         <v>25</v>
@@ -1112,62 +1113,50 @@
       <c r="F23">
         <v>25</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H23">
-        <f>501-0.2*100</f>
-        <v>481</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24">
-        <f>521-0.2*120</f>
-        <v>497</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -1241,26 +1230,26 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" t="s">
         <v>98</v>
-      </c>
-      <c r="B39" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
         <v>101</v>
-      </c>
-      <c r="B41" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1301,8 +1290,8 @@
       <c r="A47" t="s">
         <v>66</v>
       </c>
-      <c r="B47">
-        <v>120</v>
+      <c r="B47" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -1310,20 +1299,20 @@
         <v>67</v>
       </c>
       <c r="B48">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -1331,7 +1320,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>71</v>
       </c>
@@ -1339,50 +1328,59 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>72</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>74</v>
       </c>
@@ -1390,7 +1388,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>75</v>
       </c>
@@ -1398,12 +1396,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -1516,15 +1514,15 @@
         <v>95</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
